--- a/tables/chapter2_abbreviations.xlsx
+++ b/tables/chapter2_abbreviations.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>Term</t>
   </si>
@@ -101,7 +101,7 @@
     <t>GRF</t>
   </si>
   <si>
-    <t>Night-Time Light(s)</t>
+    <t>Nighttime Light(s)</t>
   </si>
   <si>
     <t>NTL</t>
@@ -183,6 +183,12 @@
   </si>
   <si>
     <t>LiDAR</t>
+  </si>
+  <si>
+    <t>Visible Infrared Imaging Radiometer Suite</t>
+  </si>
+  <si>
+    <t>VIIRS</t>
   </si>
 </sst>
 </file>
@@ -1179,7 +1185,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="51.2222222222222" customWidth="1"/>
@@ -1393,6 +1399,14 @@
         <v>51</v>
       </c>
     </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" t="s">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
